--- a/output/vendor_performance.xlsx
+++ b/output/vendor_performance.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="362">
   <si>
     <t>Beacon Fasteners — Vendor Performance</t>
   </si>
@@ -48,10 +48,10 @@
     <t>Overall required-date OTD</t>
   </si>
   <si>
-    <t>Current month</t>
-  </si>
-  <si>
-    <t>2026-05 PARTIAL (receipts through 2026-05-17)</t>
+    <t>Partial months</t>
+  </si>
+  <si>
+    <t>2025-09 PARTIAL (extract starts 2025-09-06); 2026-05 PARTIAL (receipts through 2026-05-17)</t>
   </si>
   <si>
     <t>Received value by month</t>
@@ -69,6 +69,9 @@
     <t>2025-09</t>
   </si>
   <si>
+    <t>PARTIAL</t>
+  </si>
+  <si>
     <t>2025-10</t>
   </si>
   <si>
@@ -93,9 +96,6 @@
     <t>2026-05</t>
   </si>
   <si>
-    <t>PARTIAL</t>
-  </si>
-  <si>
     <t>Required-date OTD by vendor</t>
   </si>
   <si>
@@ -1041,7 +1041,7 @@
     <t>8. MRP messages are part-level and are not used as a core vendor-performance metric (vendor attribution is ambiguous).</t>
   </si>
   <si>
-    <t>9. May 2026 historical data is PARTIAL through the analysis-as-of date 2026-05-17.</t>
+    <t>9. Boundary months 2025-09 and 2026-05 are PARTIAL: the extract starts 2025-09-06 and ends 2026-05-17. Dollar values are the receipts that exist in those months; they are not annualized.</t>
   </si>
   <si>
     <t>10. New vendor part mappings are PROPOSED unless historical evidence_count &gt;= 3 and purity &gt;= 0.95.</t>
@@ -1282,10 +1282,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2290,80 +2290,82 @@
       <c r="B13" s="11">
         <v>114453.14</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="11">
+        <v>15</v>
+      </c>
+      <c r="B14" s="12">
         <v>3533227.93</v>
       </c>
       <c r="C14" s="10"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="11">
+        <v>16</v>
+      </c>
+      <c r="B15" s="12">
         <v>4785787.08</v>
       </c>
       <c r="C15" s="10"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="11">
+        <v>17</v>
+      </c>
+      <c r="B16" s="12">
         <v>3668417.52</v>
       </c>
       <c r="C16" s="10"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="11">
+        <v>18</v>
+      </c>
+      <c r="B17" s="12">
         <v>5091552.47</v>
       </c>
       <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="11">
+        <v>19</v>
+      </c>
+      <c r="B18" s="12">
         <v>3126206.31</v>
       </c>
       <c r="C18" s="10"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="11">
+        <v>20</v>
+      </c>
+      <c r="B19" s="12">
         <v>3722784.93</v>
       </c>
       <c r="C19" s="10"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="11">
+        <v>21</v>
+      </c>
+      <c r="B20" s="12">
         <v>3223456.87</v>
       </c>
       <c r="C20" s="10"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="12">
+        <v>22</v>
+      </c>
+      <c r="B21" s="11">
         <v>930853.62</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2577,7 +2579,7 @@
       <c r="B2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>1508567.4</v>
       </c>
       <c r="D2" s="15">
@@ -2627,7 +2629,7 @@
       <c r="B3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="12">
         <v>867316.8</v>
       </c>
       <c r="D3" s="15">
@@ -2677,7 +2679,7 @@
       <c r="B4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="12">
         <v>1721393.87</v>
       </c>
       <c r="D4" s="15">
@@ -2727,7 +2729,7 @@
       <c r="B5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="12">
         <v>23978261.68</v>
       </c>
       <c r="D5" s="15">
@@ -2777,7 +2779,7 @@
       <c r="B6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="12">
         <v>107952</v>
       </c>
       <c r="D6" s="15">
@@ -2827,7 +2829,7 @@
       <c r="B7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="12">
         <v>13248.12</v>
       </c>
       <c r="D7" s="15">
@@ -2916,80 +2918,82 @@
       <c r="B2" s="11">
         <v>114453.14</v>
       </c>
-      <c r="C2" s="10"/>
+      <c r="C2" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="11">
+        <v>15</v>
+      </c>
+      <c r="B3" s="12">
         <v>3533227.93</v>
       </c>
       <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="11">
+        <v>16</v>
+      </c>
+      <c r="B4" s="12">
         <v>4785787.08</v>
       </c>
       <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="11">
+        <v>17</v>
+      </c>
+      <c r="B5" s="12">
         <v>3668417.52</v>
       </c>
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="11">
+        <v>18</v>
+      </c>
+      <c r="B6" s="12">
         <v>5091552.47</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="11">
+        <v>19</v>
+      </c>
+      <c r="B7" s="12">
         <v>3126206.31</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="11">
+        <v>20</v>
+      </c>
+      <c r="B8" s="12">
         <v>3722784.93</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="11">
+        <v>21</v>
+      </c>
+      <c r="B9" s="12">
         <v>3223456.87</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="12">
+        <v>22</v>
+      </c>
+      <c r="B10" s="11">
         <v>930853.62</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3086,7 +3090,7 @@
       <c r="K2" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="12">
         <v>477157.5</v>
       </c>
     </row>
@@ -3120,7 +3124,7 @@
       <c r="K3" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="12">
         <v>865.2</v>
       </c>
     </row>
@@ -3154,7 +3158,7 @@
       <c r="K4" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="12">
         <v>4934.4</v>
       </c>
     </row>
@@ -3188,7 +3192,7 @@
       <c r="K5" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="12">
         <v>13647.48</v>
       </c>
     </row>
@@ -3222,7 +3226,7 @@
       <c r="K6" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="12">
         <v>5548.94</v>
       </c>
     </row>
@@ -3254,7 +3258,7 @@
       <c r="K7" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="12">
         <v>867.72</v>
       </c>
     </row>
@@ -3286,7 +3290,7 @@
       <c r="K8" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3320,7 +3324,7 @@
       <c r="K9" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="12">
         <v>41.28</v>
       </c>
     </row>
@@ -3354,7 +3358,7 @@
       <c r="K10" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="12">
         <v>10938.4</v>
       </c>
     </row>
@@ -3386,7 +3390,7 @@
       <c r="K11" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="12">
         <v>24676</v>
       </c>
     </row>
@@ -3420,7 +3424,7 @@
       <c r="K12" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="12">
         <v>68</v>
       </c>
     </row>
@@ -3454,7 +3458,7 @@
       <c r="K13" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="12">
         <v>2882.4</v>
       </c>
     </row>
@@ -3488,7 +3492,7 @@
       <c r="K14" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="12">
         <v>138307.5</v>
       </c>
     </row>
@@ -3522,7 +3526,7 @@
       <c r="K15" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="12">
         <v>34.14</v>
       </c>
     </row>
@@ -3556,7 +3560,7 @@
       <c r="K16" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="12">
         <v>825.58</v>
       </c>
     </row>
@@ -3590,7 +3594,7 @@
       <c r="K17" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="12">
         <v>4430.25</v>
       </c>
     </row>
@@ -3622,7 +3626,7 @@
       <c r="K18" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3656,7 +3660,7 @@
       <c r="K19" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="12">
         <v>7386.12</v>
       </c>
     </row>
@@ -3690,7 +3694,7 @@
       <c r="K20" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="12">
         <v>14514.36</v>
       </c>
     </row>
@@ -3724,7 +3728,7 @@
       <c r="K21" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="12">
         <v>33.48</v>
       </c>
     </row>
@@ -3758,7 +3762,7 @@
       <c r="K22" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="12">
         <v>400.52</v>
       </c>
     </row>
@@ -3792,7 +3796,7 @@
       <c r="K23" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L23" s="11">
+      <c r="L23" s="12">
         <v>14164.5</v>
       </c>
     </row>
@@ -3826,7 +3830,7 @@
       <c r="K24" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L24" s="11">
+      <c r="L24" s="12">
         <v>84068.32000000001</v>
       </c>
     </row>
@@ -3860,7 +3864,7 @@
       <c r="K25" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L25" s="11">
+      <c r="L25" s="12">
         <v>66667.5</v>
       </c>
     </row>
@@ -3892,7 +3896,7 @@
       <c r="K26" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L26" s="11">
+      <c r="L26" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3924,7 +3928,7 @@
       <c r="K27" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L27" s="11">
+      <c r="L27" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3956,7 +3960,7 @@
       <c r="K28" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L28" s="11">
+      <c r="L28" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3990,7 +3994,7 @@
       <c r="K29" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L29" s="11">
+      <c r="L29" s="12">
         <v>790.46</v>
       </c>
     </row>
@@ -4024,7 +4028,7 @@
       <c r="K30" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L30" s="11">
+      <c r="L30" s="12">
         <v>61057.92</v>
       </c>
     </row>
@@ -4058,7 +4062,7 @@
       <c r="K31" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L31" s="11">
+      <c r="L31" s="12">
         <v>88.16</v>
       </c>
     </row>
@@ -4092,7 +4096,7 @@
       <c r="K32" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L32" s="11">
+      <c r="L32" s="12">
         <v>160084.96</v>
       </c>
     </row>
@@ -4126,7 +4130,7 @@
       <c r="K33" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L33" s="11">
+      <c r="L33" s="12">
         <v>1222.1</v>
       </c>
     </row>
@@ -4164,7 +4168,7 @@
       <c r="K34" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L34" s="11">
+      <c r="L34" s="12">
         <v>4320</v>
       </c>
     </row>
@@ -4202,7 +4206,7 @@
       <c r="K35" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L35" s="11">
+      <c r="L35" s="12">
         <v>13920</v>
       </c>
     </row>
@@ -4240,7 +4244,7 @@
       <c r="K36" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L36" s="11">
+      <c r="L36" s="12">
         <v>5440</v>
       </c>
     </row>
@@ -4278,7 +4282,7 @@
       <c r="K37" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L37" s="11">
+      <c r="L37" s="12">
         <v>1760</v>
       </c>
     </row>
@@ -4316,7 +4320,7 @@
       <c r="K38" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L38" s="11">
+      <c r="L38" s="12">
         <v>27435</v>
       </c>
     </row>
@@ -4354,7 +4358,7 @@
       <c r="K39" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L39" s="11">
+      <c r="L39" s="12">
         <v>8400</v>
       </c>
     </row>
@@ -4392,7 +4396,7 @@
       <c r="K40" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L40" s="11">
+      <c r="L40" s="12">
         <v>14725</v>
       </c>
     </row>
@@ -4430,7 +4434,7 @@
       <c r="K41" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L41" s="11">
+      <c r="L41" s="12">
         <v>18240</v>
       </c>
     </row>
@@ -4468,7 +4472,7 @@
       <c r="K42" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L42" s="11">
+      <c r="L42" s="12">
         <v>3760</v>
       </c>
     </row>
@@ -4506,7 +4510,7 @@
       <c r="K43" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L43" s="11">
+      <c r="L43" s="12">
         <v>11840</v>
       </c>
     </row>
@@ -4544,7 +4548,7 @@
       <c r="K44" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L44" s="11">
+      <c r="L44" s="12">
         <v>10920</v>
       </c>
     </row>
@@ -4582,7 +4586,7 @@
       <c r="K45" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L45" s="11">
+      <c r="L45" s="12">
         <v>2400</v>
       </c>
     </row>
@@ -4620,7 +4624,7 @@
       <c r="K46" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L46" s="11">
+      <c r="L46" s="12">
         <v>12320</v>
       </c>
     </row>
@@ -4658,7 +4662,7 @@
       <c r="K47" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L47" s="11">
+      <c r="L47" s="12">
         <v>23640</v>
       </c>
     </row>
@@ -4696,7 +4700,7 @@
       <c r="K48" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L48" s="11">
+      <c r="L48" s="12">
         <v>13680</v>
       </c>
     </row>
@@ -4734,7 +4738,7 @@
       <c r="K49" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L49" s="11">
+      <c r="L49" s="12">
         <v>15035</v>
       </c>
     </row>
@@ -4772,7 +4776,7 @@
       <c r="K50" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L50" s="11">
+      <c r="L50" s="12">
         <v>3600</v>
       </c>
     </row>
@@ -4810,7 +4814,7 @@
       <c r="K51" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L51" s="11">
+      <c r="L51" s="12">
         <v>9765</v>
       </c>
     </row>
@@ -4844,7 +4848,7 @@
       <c r="K52" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L52" s="11">
+      <c r="L52" s="12">
         <v>70928.48</v>
       </c>
     </row>
@@ -4882,7 +4886,7 @@
       <c r="K53" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L53" s="11">
+      <c r="L53" s="12">
         <v>23405</v>
       </c>
     </row>
@@ -4920,7 +4924,7 @@
       <c r="K54" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L54" s="11">
+      <c r="L54" s="12">
         <v>3440</v>
       </c>
     </row>
@@ -4954,7 +4958,7 @@
       <c r="K55" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L55" s="11">
+      <c r="L55" s="12">
         <v>4320</v>
       </c>
     </row>
@@ -4986,7 +4990,7 @@
       <c r="K56" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L56" s="11">
+      <c r="L56" s="12">
         <v>100.5</v>
       </c>
     </row>
@@ -5024,7 +5028,7 @@
       <c r="K57" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L57" s="11">
+      <c r="L57" s="12">
         <v>17360</v>
       </c>
     </row>
@@ -5062,7 +5066,7 @@
       <c r="K58" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L58" s="11">
+      <c r="L58" s="12">
         <v>20520</v>
       </c>
     </row>
@@ -5100,7 +5104,7 @@
       <c r="K59" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L59" s="11">
+      <c r="L59" s="12">
         <v>17040</v>
       </c>
     </row>
@@ -5138,7 +5142,7 @@
       <c r="K60" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L60" s="11">
+      <c r="L60" s="12">
         <v>12720</v>
       </c>
     </row>
@@ -5176,7 +5180,7 @@
       <c r="K61" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L61" s="11">
+      <c r="L61" s="12">
         <v>9610</v>
       </c>
     </row>
@@ -5214,7 +5218,7 @@
       <c r="K62" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L62" s="11">
+      <c r="L62" s="12">
         <v>17050</v>
       </c>
     </row>
@@ -5248,7 +5252,7 @@
       <c r="K63" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L63" s="11">
+      <c r="L63" s="12">
         <v>6510</v>
       </c>
     </row>
@@ -5286,7 +5290,7 @@
       <c r="K64" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L64" s="11">
+      <c r="L64" s="12">
         <v>1200</v>
       </c>
     </row>
@@ -5320,7 +5324,7 @@
       <c r="K65" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L65" s="11">
+      <c r="L65" s="12">
         <v>5520</v>
       </c>
     </row>
@@ -5358,7 +5362,7 @@
       <c r="K66" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L66" s="11">
+      <c r="L66" s="12">
         <v>7440</v>
       </c>
     </row>
@@ -5396,7 +5400,7 @@
       <c r="K67" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L67" s="11">
+      <c r="L67" s="12">
         <v>8040</v>
       </c>
     </row>
@@ -5434,7 +5438,7 @@
       <c r="K68" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L68" s="11">
+      <c r="L68" s="12">
         <v>16120</v>
       </c>
     </row>
@@ -5472,7 +5476,7 @@
       <c r="K69" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L69" s="11">
+      <c r="L69" s="12">
         <v>8835</v>
       </c>
     </row>
@@ -5506,7 +5510,7 @@
       <c r="K70" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L70" s="11">
+      <c r="L70" s="12">
         <v>7914.5</v>
       </c>
     </row>
@@ -5540,7 +5544,7 @@
       <c r="K71" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L71" s="11">
+      <c r="L71" s="12">
         <v>10640</v>
       </c>
     </row>
@@ -5578,7 +5582,7 @@
       <c r="K72" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L72" s="11">
+      <c r="L72" s="12">
         <v>9455</v>
       </c>
     </row>
@@ -5616,7 +5620,7 @@
       <c r="K73" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L73" s="11">
+      <c r="L73" s="12">
         <v>21855</v>
       </c>
     </row>
@@ -5650,7 +5654,7 @@
       <c r="K74" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L74" s="11">
+      <c r="L74" s="12">
         <v>13330</v>
       </c>
     </row>
@@ -5688,7 +5692,7 @@
       <c r="K75" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L75" s="11">
+      <c r="L75" s="12">
         <v>5160</v>
       </c>
     </row>
@@ -5720,7 +5724,7 @@
       <c r="K76" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L76" s="11">
+      <c r="L76" s="12">
         <v>923.3</v>
       </c>
     </row>
@@ -5758,7 +5762,7 @@
       <c r="K77" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L77" s="11">
+      <c r="L77" s="12">
         <v>11040</v>
       </c>
     </row>
@@ -5796,7 +5800,7 @@
       <c r="K78" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L78" s="11">
+      <c r="L78" s="12">
         <v>8400</v>
       </c>
     </row>
@@ -5834,7 +5838,7 @@
       <c r="K79" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L79" s="11">
+      <c r="L79" s="12">
         <v>13200</v>
       </c>
     </row>
@@ -5872,7 +5876,7 @@
       <c r="K80" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L80" s="11">
+      <c r="L80" s="12">
         <v>2880</v>
       </c>
     </row>
@@ -5910,7 +5914,7 @@
       <c r="K81" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L81" s="11">
+      <c r="L81" s="12">
         <v>7080</v>
       </c>
     </row>
@@ -5948,7 +5952,7 @@
       <c r="K82" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L82" s="11">
+      <c r="L82" s="12">
         <v>8835</v>
       </c>
     </row>
@@ -5986,7 +5990,7 @@
       <c r="K83" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L83" s="11">
+      <c r="L83" s="12">
         <v>6045</v>
       </c>
     </row>
@@ -6024,7 +6028,7 @@
       <c r="K84" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L84" s="11">
+      <c r="L84" s="12">
         <v>15120</v>
       </c>
     </row>
@@ -6062,7 +6066,7 @@
       <c r="K85" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L85" s="11">
+      <c r="L85" s="12">
         <v>3240</v>
       </c>
     </row>
@@ -6100,7 +6104,7 @@
       <c r="K86" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L86" s="11">
+      <c r="L86" s="12">
         <v>18480</v>
       </c>
     </row>
@@ -6138,7 +6142,7 @@
       <c r="K87" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L87" s="11">
+      <c r="L87" s="12">
         <v>775</v>
       </c>
     </row>
@@ -6172,7 +6176,7 @@
       <c r="K88" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L88" s="11">
+      <c r="L88" s="12">
         <v>13175</v>
       </c>
     </row>
@@ -6210,7 +6214,7 @@
       <c r="K89" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L89" s="11">
+      <c r="L89" s="12">
         <v>11780</v>
       </c>
     </row>
@@ -6244,7 +6248,7 @@
       <c r="K90" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L90" s="11">
+      <c r="L90" s="12">
         <v>1375</v>
       </c>
     </row>
@@ -6282,7 +6286,7 @@
       <c r="K91" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L91" s="11">
+      <c r="L91" s="12">
         <v>4160</v>
       </c>
     </row>
@@ -6320,7 +6324,7 @@
       <c r="K92" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L92" s="11">
+      <c r="L92" s="12">
         <v>11625</v>
       </c>
     </row>
@@ -6354,7 +6358,7 @@
       <c r="K93" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L93" s="11">
+      <c r="L93" s="12">
         <v>6665</v>
       </c>
     </row>
@@ -6388,7 +6392,7 @@
       <c r="K94" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L94" s="11">
+      <c r="L94" s="12">
         <v>15200</v>
       </c>
     </row>
@@ -6420,7 +6424,7 @@
       <c r="K95" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L95" s="11">
+      <c r="L95" s="12">
         <v>0</v>
       </c>
     </row>
@@ -6458,7 +6462,7 @@
       <c r="K96" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L96" s="11">
+      <c r="L96" s="12">
         <v>11600</v>
       </c>
     </row>
@@ -6496,7 +6500,7 @@
       <c r="K97" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L97" s="11">
+      <c r="L97" s="12">
         <v>17515</v>
       </c>
     </row>
@@ -6534,7 +6538,7 @@
       <c r="K98" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L98" s="11">
+      <c r="L98" s="12">
         <v>720</v>
       </c>
     </row>
@@ -6572,7 +6576,7 @@
       <c r="K99" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L99" s="11">
+      <c r="L99" s="12">
         <v>7200</v>
       </c>
     </row>
@@ -6604,7 +6608,7 @@
       <c r="K100" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L100" s="11">
+      <c r="L100" s="12">
         <v>0</v>
       </c>
     </row>
@@ -6642,7 +6646,7 @@
       <c r="K101" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L101" s="11">
+      <c r="L101" s="12">
         <v>4059</v>
       </c>
     </row>
@@ -6680,7 +6684,7 @@
       <c r="K102" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L102" s="11">
+      <c r="L102" s="12">
         <v>11000</v>
       </c>
     </row>
@@ -6714,7 +6718,7 @@
       <c r="K103" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L103" s="11">
+      <c r="L103" s="12">
         <v>193500</v>
       </c>
     </row>
@@ -6752,7 +6756,7 @@
       <c r="K104" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L104" s="11">
+      <c r="L104" s="12">
         <v>5208</v>
       </c>
     </row>
@@ -6790,7 +6794,7 @@
       <c r="K105" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L105" s="11">
+      <c r="L105" s="12">
         <v>2542</v>
       </c>
     </row>
@@ -6828,7 +6832,7 @@
       <c r="K106" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L106" s="11">
+      <c r="L106" s="12">
         <v>21070</v>
       </c>
     </row>
@@ -6866,7 +6870,7 @@
       <c r="K107" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L107" s="11">
+      <c r="L107" s="12">
         <v>15252</v>
       </c>
     </row>
@@ -6900,7 +6904,7 @@
       <c r="K108" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L108" s="11">
+      <c r="L108" s="12">
         <v>5664</v>
       </c>
     </row>
@@ -6938,7 +6942,7 @@
       <c r="K109" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L109" s="11">
+      <c r="L109" s="12">
         <v>55107</v>
       </c>
     </row>
@@ -6976,7 +6980,7 @@
       <c r="K110" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L110" s="11">
+      <c r="L110" s="12">
         <v>137200</v>
       </c>
     </row>
@@ -7010,7 +7014,7 @@
       <c r="K111" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L111" s="11">
+      <c r="L111" s="12">
         <v>7462</v>
       </c>
     </row>
@@ -7048,7 +7052,7 @@
       <c r="K112" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L112" s="11">
+      <c r="L112" s="12">
         <v>3080</v>
       </c>
     </row>
@@ -7086,7 +7090,7 @@
       <c r="K113" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L113" s="11">
+      <c r="L113" s="12">
         <v>15004</v>
       </c>
     </row>
@@ -7124,7 +7128,7 @@
       <c r="K114" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L114" s="11">
+      <c r="L114" s="12">
         <v>1092</v>
       </c>
     </row>
@@ -7162,7 +7166,7 @@
       <c r="K115" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L115" s="11">
+      <c r="L115" s="12">
         <v>8200</v>
       </c>
     </row>
@@ -7200,7 +7204,7 @@
       <c r="K116" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L116" s="11">
+      <c r="L116" s="12">
         <v>47120</v>
       </c>
     </row>
@@ -7238,7 +7242,7 @@
       <c r="K117" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L117" s="11">
+      <c r="L117" s="12">
         <v>12840</v>
       </c>
     </row>
@@ -7272,7 +7276,7 @@
       <c r="K118" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L118" s="11">
+      <c r="L118" s="12">
         <v>8400</v>
       </c>
     </row>
@@ -7310,7 +7314,7 @@
       <c r="K119" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L119" s="11">
+      <c r="L119" s="12">
         <v>6200</v>
       </c>
     </row>
@@ -7348,7 +7352,7 @@
       <c r="K120" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L120" s="11">
+      <c r="L120" s="12">
         <v>5360</v>
       </c>
     </row>
@@ -7380,7 +7384,7 @@
       <c r="K121" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L121" s="11">
+      <c r="L121" s="12">
         <v>20354.6</v>
       </c>
     </row>
@@ -7414,7 +7418,7 @@
       <c r="K122" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L122" s="11">
+      <c r="L122" s="12">
         <v>1840</v>
       </c>
     </row>
@@ -7452,7 +7456,7 @@
       <c r="K123" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L123" s="11">
+      <c r="L123" s="12">
         <v>5124</v>
       </c>
     </row>
@@ -7490,7 +7494,7 @@
       <c r="K124" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L124" s="11">
+      <c r="L124" s="12">
         <v>12925</v>
       </c>
     </row>
@@ -7528,7 +7532,7 @@
       <c r="K125" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L125" s="11">
+      <c r="L125" s="12">
         <v>1925</v>
       </c>
     </row>
@@ -7566,7 +7570,7 @@
       <c r="K126" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L126" s="11">
+      <c r="L126" s="12">
         <v>11935</v>
       </c>
     </row>
@@ -7604,7 +7608,7 @@
       <c r="K127" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L127" s="11">
+      <c r="L127" s="12">
         <v>7865</v>
       </c>
     </row>
@@ -7642,7 +7646,7 @@
       <c r="K128" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L128" s="11">
+      <c r="L128" s="12">
         <v>6820</v>
       </c>
     </row>
@@ -7680,7 +7684,7 @@
       <c r="K129" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L129" s="11">
+      <c r="L129" s="12">
         <v>715</v>
       </c>
     </row>
@@ -7712,7 +7716,7 @@
       <c r="K130" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L130" s="11">
+      <c r="L130" s="12">
         <v>0</v>
       </c>
     </row>
@@ -7750,7 +7754,7 @@
       <c r="K131" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L131" s="11">
+      <c r="L131" s="12">
         <v>600.6</v>
       </c>
     </row>
@@ -7788,7 +7792,7 @@
       <c r="K132" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L132" s="11">
+      <c r="L132" s="12">
         <v>3648</v>
       </c>
     </row>
@@ -7826,7 +7830,7 @@
       <c r="K133" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L133" s="11">
+      <c r="L133" s="12">
         <v>411750</v>
       </c>
     </row>
@@ -7864,7 +7868,7 @@
       <c r="K134" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L134" s="11">
+      <c r="L134" s="12">
         <v>6555</v>
       </c>
     </row>
@@ -7902,7 +7906,7 @@
       <c r="K135" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L135" s="11">
+      <c r="L135" s="12">
         <v>13950</v>
       </c>
     </row>
@@ -7940,7 +7944,7 @@
       <c r="K136" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L136" s="11">
+      <c r="L136" s="12">
         <v>1860</v>
       </c>
     </row>
@@ -7978,7 +7982,7 @@
       <c r="K137" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L137" s="11">
+      <c r="L137" s="12">
         <v>22920</v>
       </c>
     </row>
@@ -8012,7 +8016,7 @@
       <c r="K138" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L138" s="11">
+      <c r="L138" s="12">
         <v>8580</v>
       </c>
     </row>
@@ -8050,7 +8054,7 @@
       <c r="K139" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L139" s="11">
+      <c r="L139" s="12">
         <v>3135</v>
       </c>
     </row>
@@ -8088,7 +8092,7 @@
       <c r="K140" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L140" s="11">
+      <c r="L140" s="12">
         <v>2952</v>
       </c>
     </row>
@@ -8126,7 +8130,7 @@
       <c r="K141" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L141" s="11">
+      <c r="L141" s="12">
         <v>3440</v>
       </c>
     </row>
@@ -8164,7 +8168,7 @@
       <c r="K142" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L142" s="11">
+      <c r="L142" s="12">
         <v>5740</v>
       </c>
     </row>
@@ -8202,7 +8206,7 @@
       <c r="K143" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L143" s="11">
+      <c r="L143" s="12">
         <v>12210</v>
       </c>
     </row>
@@ -8240,7 +8244,7 @@
       <c r="K144" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L144" s="11">
+      <c r="L144" s="12">
         <v>10578</v>
       </c>
     </row>
@@ -8278,7 +8282,7 @@
       <c r="K145" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L145" s="11">
+      <c r="L145" s="12">
         <v>13330</v>
       </c>
     </row>
@@ -8316,7 +8320,7 @@
       <c r="K146" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L146" s="11">
+      <c r="L146" s="12">
         <v>930</v>
       </c>
     </row>
@@ -8350,7 +8354,7 @@
       <c r="K147" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L147" s="11">
+      <c r="L147" s="12">
         <v>5995</v>
       </c>
     </row>
@@ -8384,7 +8388,7 @@
       <c r="K148" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L148" s="11">
+      <c r="L148" s="12">
         <v>984.5</v>
       </c>
     </row>
@@ -8422,7 +8426,7 @@
       <c r="K149" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L149" s="11">
+      <c r="L149" s="12">
         <v>731.5</v>
       </c>
     </row>
@@ -8460,7 +8464,7 @@
       <c r="K150" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L150" s="11">
+      <c r="L150" s="12">
         <v>70680</v>
       </c>
     </row>
@@ -8498,7 +8502,7 @@
       <c r="K151" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L151" s="11">
+      <c r="L151" s="12">
         <v>23560</v>
       </c>
     </row>
@@ -8536,7 +8540,7 @@
       <c r="K152" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L152" s="11">
+      <c r="L152" s="12">
         <v>42160</v>
       </c>
     </row>
@@ -8574,7 +8578,7 @@
       <c r="K153" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L153" s="11">
+      <c r="L153" s="12">
         <v>1073.8</v>
       </c>
     </row>
@@ -8612,7 +8616,7 @@
       <c r="K154" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L154" s="11">
+      <c r="L154" s="12">
         <v>7056</v>
       </c>
     </row>
@@ -8650,7 +8654,7 @@
       <c r="K155" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L155" s="11">
+      <c r="L155" s="12">
         <v>55578</v>
       </c>
     </row>
@@ -8688,7 +8692,7 @@
       <c r="K156" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L156" s="11">
+      <c r="L156" s="12">
         <v>91728</v>
       </c>
     </row>
@@ -8726,7 +8730,7 @@
       <c r="K157" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L157" s="11">
+      <c r="L157" s="12">
         <v>105504</v>
       </c>
     </row>
@@ -8764,7 +8768,7 @@
       <c r="K158" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L158" s="11">
+      <c r="L158" s="12">
         <v>9016</v>
       </c>
     </row>
@@ -8802,7 +8806,7 @@
       <c r="K159" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L159" s="11">
+      <c r="L159" s="12">
         <v>27832</v>
       </c>
     </row>
@@ -8840,7 +8844,7 @@
       <c r="K160" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L160" s="11">
+      <c r="L160" s="12">
         <v>52528</v>
       </c>
     </row>
@@ -8878,7 +8882,7 @@
       <c r="K161" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L161" s="11">
+      <c r="L161" s="12">
         <v>22165</v>
       </c>
     </row>
@@ -8912,7 +8916,7 @@
       <c r="K162" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L162" s="11">
+      <c r="L162" s="12">
         <v>9600</v>
       </c>
     </row>
@@ -8946,7 +8950,7 @@
       <c r="K163" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L163" s="11">
+      <c r="L163" s="12">
         <v>3680</v>
       </c>
     </row>
@@ -8984,7 +8988,7 @@
       <c r="K164" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L164" s="11">
+      <c r="L164" s="12">
         <v>6000</v>
       </c>
     </row>
@@ -9016,7 +9020,7 @@
       <c r="K165" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L165" s="11">
+      <c r="L165" s="12">
         <v>0</v>
       </c>
     </row>
@@ -9054,7 +9058,7 @@
       <c r="K166" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L166" s="11">
+      <c r="L166" s="12">
         <v>14280</v>
       </c>
     </row>
@@ -9092,7 +9096,7 @@
       <c r="K167" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L167" s="11">
+      <c r="L167" s="12">
         <v>24955</v>
       </c>
     </row>
@@ -9130,7 +9134,7 @@
       <c r="K168" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L168" s="11">
+      <c r="L168" s="12">
         <v>5766</v>
       </c>
     </row>
@@ -9168,7 +9172,7 @@
       <c r="K169" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L169" s="11">
+      <c r="L169" s="12">
         <v>11696</v>
       </c>
     </row>
@@ -9206,7 +9210,7 @@
       <c r="K170" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L170" s="11">
+      <c r="L170" s="12">
         <v>11346</v>
       </c>
     </row>
@@ -9244,7 +9248,7 @@
       <c r="K171" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L171" s="11">
+      <c r="L171" s="12">
         <v>6622</v>
       </c>
     </row>
@@ -9282,7 +9286,7 @@
       <c r="K172" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L172" s="11">
+      <c r="L172" s="12">
         <v>688</v>
       </c>
     </row>
@@ -9320,7 +9324,7 @@
       <c r="K173" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L173" s="11">
+      <c r="L173" s="12">
         <v>12485</v>
       </c>
     </row>
@@ -9358,7 +9362,7 @@
       <c r="K174" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L174" s="11">
+      <c r="L174" s="12">
         <v>9240</v>
       </c>
     </row>
@@ -9392,7 +9396,7 @@
       <c r="K175" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L175" s="11">
+      <c r="L175" s="12">
         <v>9240</v>
       </c>
     </row>
@@ -9430,7 +9434,7 @@
       <c r="K176" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L176" s="11">
+      <c r="L176" s="12">
         <v>14818</v>
       </c>
     </row>
@@ -9468,7 +9472,7 @@
       <c r="K177" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L177" s="11">
+      <c r="L177" s="12">
         <v>14364</v>
       </c>
     </row>
@@ -9506,7 +9510,7 @@
       <c r="K178" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L178" s="11">
+      <c r="L178" s="12">
         <v>15738</v>
       </c>
     </row>
@@ -9544,7 +9548,7 @@
       <c r="K179" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L179" s="11">
+      <c r="L179" s="12">
         <v>6435</v>
       </c>
     </row>
@@ -9578,7 +9582,7 @@
       <c r="K180" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L180" s="11">
+      <c r="L180" s="12">
         <v>19006</v>
       </c>
     </row>
@@ -9616,7 +9620,7 @@
       <c r="K181" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L181" s="11">
+      <c r="L181" s="12">
         <v>8556</v>
       </c>
     </row>
@@ -9654,7 +9658,7 @@
       <c r="K182" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L182" s="11">
+      <c r="L182" s="12">
         <v>748</v>
       </c>
     </row>
@@ -9686,7 +9690,7 @@
       <c r="K183" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L183" s="11">
+      <c r="L183" s="12">
         <v>0</v>
       </c>
     </row>
@@ -9724,7 +9728,7 @@
       <c r="K184" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L184" s="11">
+      <c r="L184" s="12">
         <v>577.5</v>
       </c>
     </row>
@@ -9758,7 +9762,7 @@
       <c r="K185" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L185" s="11">
+      <c r="L185" s="12">
         <v>1028.5</v>
       </c>
     </row>
@@ -9792,7 +9796,7 @@
       <c r="K186" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L186" s="11">
+      <c r="L186" s="12">
         <v>284</v>
       </c>
     </row>
@@ -9830,7 +9834,7 @@
       <c r="K187" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L187" s="11">
+      <c r="L187" s="12">
         <v>4032</v>
       </c>
     </row>
@@ -9868,7 +9872,7 @@
       <c r="K188" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L188" s="11">
+      <c r="L188" s="12">
         <v>1037.4</v>
       </c>
     </row>
@@ -9900,7 +9904,7 @@
       <c r="K189" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L189" s="11">
+      <c r="L189" s="12">
         <v>0</v>
       </c>
     </row>
@@ -9932,7 +9936,7 @@
       <c r="K190" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L190" s="11">
+      <c r="L190" s="12">
         <v>0</v>
       </c>
     </row>
@@ -9964,7 +9968,7 @@
       <c r="K191" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L191" s="11">
+      <c r="L191" s="12">
         <v>0</v>
       </c>
     </row>
@@ -10002,7 +10006,7 @@
       <c r="K192" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L192" s="11">
+      <c r="L192" s="12">
         <v>56715</v>
       </c>
     </row>
@@ -10040,7 +10044,7 @@
       <c r="K193" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L193" s="11">
+      <c r="L193" s="12">
         <v>28260</v>
       </c>
     </row>
@@ -10078,7 +10082,7 @@
       <c r="K194" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L194" s="11">
+      <c r="L194" s="12">
         <v>25872</v>
       </c>
     </row>
@@ -10116,7 +10120,7 @@
       <c r="K195" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L195" s="11">
+      <c r="L195" s="12">
         <v>36195</v>
       </c>
     </row>
@@ -10154,7 +10158,7 @@
       <c r="K196" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L196" s="11">
+      <c r="L196" s="12">
         <v>106624</v>
       </c>
     </row>
@@ -10192,7 +10196,7 @@
       <c r="K197" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L197" s="11">
+      <c r="L197" s="12">
         <v>58500</v>
       </c>
     </row>
@@ -10230,7 +10234,7 @@
       <c r="K198" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L198" s="11">
+      <c r="L198" s="12">
         <v>141904</v>
       </c>
     </row>
@@ -10268,7 +10272,7 @@
       <c r="K199" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L199" s="11">
+      <c r="L199" s="12">
         <v>123872</v>
       </c>
     </row>
@@ -10306,7 +10310,7 @@
       <c r="K200" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L200" s="11">
+      <c r="L200" s="12">
         <v>63504</v>
       </c>
     </row>
@@ -10344,7 +10348,7 @@
       <c r="K201" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L201" s="11">
+      <c r="L201" s="12">
         <v>36267</v>
       </c>
     </row>
@@ -10382,7 +10386,7 @@
       <c r="K202" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L202" s="11">
+      <c r="L202" s="12">
         <v>234000</v>
       </c>
     </row>
@@ -10416,7 +10420,7 @@
       <c r="K203" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L203" s="11">
+      <c r="L203" s="12">
         <v>7840</v>
       </c>
     </row>
@@ -10454,7 +10458,7 @@
       <c r="K204" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L204" s="11">
+      <c r="L204" s="12">
         <v>247500</v>
       </c>
     </row>
@@ -10492,7 +10496,7 @@
       <c r="K205" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L205" s="11">
+      <c r="L205" s="12">
         <v>68115</v>
       </c>
     </row>
@@ -10530,7 +10534,7 @@
       <c r="K206" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L206" s="11">
+      <c r="L206" s="12">
         <v>28616</v>
       </c>
     </row>
@@ -10568,7 +10572,7 @@
       <c r="K207" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L207" s="11">
+      <c r="L207" s="12">
         <v>82896</v>
       </c>
     </row>
@@ -10606,7 +10610,7 @@
       <c r="K208" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L208" s="11">
+      <c r="L208" s="12">
         <v>3100</v>
       </c>
     </row>
@@ -10644,7 +10648,7 @@
       <c r="K209" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L209" s="11">
+      <c r="L209" s="12">
         <v>17670</v>
       </c>
     </row>
@@ -10682,7 +10686,7 @@
       <c r="K210" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L210" s="11">
+      <c r="L210" s="12">
         <v>7831</v>
       </c>
     </row>
@@ -10720,7 +10724,7 @@
       <c r="K211" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L211" s="11">
+      <c r="L211" s="12">
         <v>11508</v>
       </c>
     </row>
@@ -10758,7 +10762,7 @@
       <c r="K212" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L212" s="11">
+      <c r="L212" s="12">
         <v>10230</v>
       </c>
     </row>
@@ -10796,7 +10800,7 @@
       <c r="K213" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L213" s="11">
+      <c r="L213" s="12">
         <v>6138</v>
       </c>
     </row>
@@ -10834,7 +10838,7 @@
       <c r="K214" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L214" s="11">
+      <c r="L214" s="12">
         <v>4715</v>
       </c>
     </row>
@@ -10868,7 +10872,7 @@
       <c r="K215" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L215" s="11">
+      <c r="L215" s="12">
         <v>13158</v>
       </c>
     </row>
@@ -10906,7 +10910,7 @@
       <c r="K216" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L216" s="11">
+      <c r="L216" s="12">
         <v>8736</v>
       </c>
     </row>
@@ -10940,7 +10944,7 @@
       <c r="K217" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L217" s="11">
+      <c r="L217" s="12">
         <v>8745</v>
       </c>
     </row>
@@ -10978,7 +10982,7 @@
       <c r="K218" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L218" s="11">
+      <c r="L218" s="12">
         <v>8308</v>
       </c>
     </row>
@@ -11016,7 +11020,7 @@
       <c r="K219" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L219" s="11">
+      <c r="L219" s="12">
         <v>5225</v>
       </c>
     </row>
@@ -11054,7 +11058,7 @@
       <c r="K220" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L220" s="11">
+      <c r="L220" s="12">
         <v>781</v>
       </c>
     </row>
@@ -11088,7 +11092,7 @@
       <c r="K221" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L221" s="11">
+      <c r="L221" s="12">
         <v>208</v>
       </c>
     </row>
@@ -11126,7 +11130,7 @@
       <c r="K222" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L222" s="11">
+      <c r="L222" s="12">
         <v>764</v>
       </c>
     </row>
@@ -11164,7 +11168,7 @@
       <c r="K223" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L223" s="11">
+      <c r="L223" s="12">
         <v>676</v>
       </c>
     </row>
@@ -11202,7 +11206,7 @@
       <c r="K224" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L224" s="11">
+      <c r="L224" s="12">
         <v>44</v>
       </c>
     </row>
@@ -11240,7 +11244,7 @@
       <c r="K225" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L225" s="11">
+      <c r="L225" s="12">
         <v>649</v>
       </c>
     </row>
@@ -11278,7 +11282,7 @@
       <c r="K226" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L226" s="11">
+      <c r="L226" s="12">
         <v>137.5</v>
       </c>
     </row>
@@ -11316,7 +11320,7 @@
       <c r="K227" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L227" s="11">
+      <c r="L227" s="12">
         <v>536</v>
       </c>
     </row>
@@ -11350,7 +11354,7 @@
       <c r="K228" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L228" s="11">
+      <c r="L228" s="12">
         <v>803</v>
       </c>
     </row>
@@ -11384,7 +11388,7 @@
       <c r="K229" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L229" s="11">
+      <c r="L229" s="12">
         <v>208</v>
       </c>
     </row>
@@ -11422,7 +11426,7 @@
       <c r="K230" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L230" s="11">
+      <c r="L230" s="12">
         <v>624</v>
       </c>
     </row>
@@ -11460,7 +11464,7 @@
       <c r="K231" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L231" s="11">
+      <c r="L231" s="12">
         <v>17360</v>
       </c>
     </row>
@@ -11498,7 +11502,7 @@
       <c r="K232" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L232" s="11">
+      <c r="L232" s="12">
         <v>418.6</v>
       </c>
     </row>
@@ -11536,7 +11540,7 @@
       <c r="K233" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L233" s="11">
+      <c r="L233" s="12">
         <v>3168</v>
       </c>
     </row>
@@ -11574,7 +11578,7 @@
       <c r="K234" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L234" s="11">
+      <c r="L234" s="12">
         <v>54.6</v>
       </c>
     </row>
@@ -11612,7 +11616,7 @@
       <c r="K235" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L235" s="11">
+      <c r="L235" s="12">
         <v>1728</v>
       </c>
     </row>
@@ -11650,7 +11654,7 @@
       <c r="K236" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L236" s="11">
+      <c r="L236" s="12">
         <v>21080</v>
       </c>
     </row>
@@ -11688,7 +11692,7 @@
       <c r="K237" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L237" s="11">
+      <c r="L237" s="12">
         <v>382.2</v>
       </c>
     </row>
@@ -11726,7 +11730,7 @@
       <c r="K238" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L238" s="11">
+      <c r="L238" s="12">
         <v>14.4</v>
       </c>
     </row>
@@ -11758,7 +11762,7 @@
       <c r="K239" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L239" s="11">
+      <c r="L239" s="12">
         <v>0</v>
       </c>
     </row>
@@ -11790,7 +11794,7 @@
       <c r="K240" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L240" s="11">
+      <c r="L240" s="12">
         <v>0</v>
       </c>
     </row>

--- a/output/vendor_performance.xlsx
+++ b/output/vendor_performance.xlsx
@@ -1008,10 +1008,10 @@
     <t>• OTD to vendor promise: evaluated only when promised_date &lt;= as-of. Same completion-date rule.</t>
   </si>
   <si>
-    <t>• Promise slippage: promised_date ? required_date (positive means vendor already committed later than Beacon asked).</t>
-  </si>
-  <si>
-    <t>• Confirmation lag: confirmation.doc_date ? po_header.po_date.</t>
+    <t>• Promise slippage: promised_date - required_date (positive means vendor already committed later than Beacon asked).</t>
+  </si>
+  <si>
+    <t>• Confirmation lag: confirmation.doc_date - po_header.po_date.</t>
   </si>
   <si>
     <t>Assumptions</t>
